--- a/数据/无人机应急物资运输基础数据/运输无人机数据.xlsx
+++ b/数据/无人机应急物资运输基础数据/运输无人机数据.xlsx
@@ -5,16 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SF_Dir\第二十三届中国研究生数学建模竞赛 - 中文题目\中文题目\D题\数据\无人机应急物资运输基础数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HH\Desktop\(南航学习资料汇总)博四下结束暑假\赛题+参考答案 - 最终版本\赛题+参考答案 - 最终版本\赛题\数据\无人机应急物资运输基础数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
-    <sheet name="三类机型参数 " sheetId="1" r:id="rId1"/>
-    <sheet name="逐架无人机清单 " sheetId="2" r:id="rId2"/>
-    <sheet name="共享电池库存 " sheetId="3" r:id="rId3"/>
+    <sheet name="数据" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +32,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三类机型参数</t>
+    </r>
+  </si>
   <si>
     <r>
       <rPr>
@@ -530,6 +540,18 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>逐架无人机清单</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
@@ -575,6 +597,18 @@
   </si>
   <si>
     <t>U08</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>共享电池库存</t>
+    </r>
   </si>
   <si>
     <r>
@@ -628,13 +662,19 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -642,12 +682,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -803,6 +844,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1114,193 +1162,193 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1773,183 +1821,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:R22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12" style="6" customWidth="1"/>
-    <col min="2" max="2" width="24" style="6" customWidth="1"/>
-    <col min="3" max="3" width="21.6" style="6" customWidth="1"/>
-    <col min="4" max="9" width="18" style="6" customWidth="1"/>
-    <col min="10" max="10" width="16" style="6" customWidth="1"/>
-    <col min="11" max="11" width="19.8" style="6" customWidth="1"/>
-    <col min="12" max="12" width="16" style="6" customWidth="1"/>
-    <col min="13" max="13" width="22.4" style="6" customWidth="1"/>
-    <col min="14" max="14" width="20.6" style="6" customWidth="1"/>
-    <col min="15" max="15" width="20" style="6" customWidth="1"/>
-    <col min="16" max="16" width="20.7" style="6" customWidth="1"/>
-    <col min="17" max="18" width="14" style="6" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6" style="1" customWidth="1"/>
+    <col min="4" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.8" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="1" customWidth="1"/>
+    <col min="13" max="13" width="22.4" style="1" customWidth="1"/>
+    <col min="14" max="14" width="20.6" style="1" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20.7" style="1" customWidth="1"/>
+    <col min="17" max="18" width="14" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" ht="25" customHeight="1" spans="1:18">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="24" customHeight="1" spans="1:18">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="25" customHeight="1" spans="1:18">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="N2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="O2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="P2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="Q2" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:18">
-      <c r="A2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="7">
-        <v>70</v>
-      </c>
-      <c r="D2" s="7">
-        <v>25</v>
-      </c>
-      <c r="E2" s="7">
-        <v>0.06</v>
-      </c>
-      <c r="F2" s="4">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4">
-        <v>25000</v>
-      </c>
-      <c r="H2" s="4">
-        <v>20000</v>
-      </c>
-      <c r="I2" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="J2" s="3">
-        <v>20</v>
-      </c>
-      <c r="K2" s="3">
-        <v>300</v>
-      </c>
-      <c r="L2" s="3">
-        <v>30</v>
-      </c>
-      <c r="M2" s="3">
-        <v>150</v>
-      </c>
-      <c r="N2" s="3">
-        <v>30</v>
-      </c>
-      <c r="O2" s="7">
-        <v>3</v>
-      </c>
-      <c r="P2" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0.72</v>
-      </c>
-      <c r="R2" s="8">
-        <v>0</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:18">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7">
-        <v>65</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="C3" s="5">
+        <v>70</v>
+      </c>
+      <c r="D3" s="5">
+        <v>25</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="F3" s="6">
+        <v>12</v>
+      </c>
+      <c r="G3" s="6">
+        <v>25000</v>
+      </c>
+      <c r="H3" s="6">
+        <v>20000</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="J3" s="7">
+        <v>20</v>
+      </c>
+      <c r="K3" s="7">
+        <v>300</v>
+      </c>
+      <c r="L3" s="7">
         <v>30</v>
       </c>
-      <c r="E3" s="7">
-        <v>0.073</v>
-      </c>
-      <c r="F3" s="4">
-        <v>15</v>
-      </c>
-      <c r="G3" s="4">
-        <v>28000</v>
-      </c>
-      <c r="H3" s="4">
-        <v>16000</v>
-      </c>
-      <c r="I3" s="7">
-        <v>4</v>
-      </c>
-      <c r="J3" s="3">
-        <v>20</v>
-      </c>
-      <c r="K3" s="3">
-        <v>300</v>
-      </c>
-      <c r="L3" s="3">
+      <c r="M3" s="7">
+        <v>150</v>
+      </c>
+      <c r="N3" s="7">
         <v>30</v>
       </c>
-      <c r="M3" s="3">
-        <v>150</v>
-      </c>
-      <c r="N3" s="3">
-        <v>30</v>
-      </c>
-      <c r="O3" s="7">
+      <c r="O3" s="5">
         <v>3</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="5">
         <v>2.5</v>
       </c>
       <c r="Q3" s="8">
@@ -1960,53 +1974,53 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:18">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7">
-        <v>69.9</v>
-      </c>
-      <c r="D4" s="7">
-        <v>80</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="C4" s="5">
+        <v>65</v>
+      </c>
+      <c r="D4" s="5">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.073</v>
+      </c>
+      <c r="F4" s="6">
         <v>15</v>
       </c>
-      <c r="G4" s="4">
-        <v>26000</v>
-      </c>
-      <c r="H4" s="4">
-        <v>12000</v>
-      </c>
-      <c r="I4" s="7">
-        <v>8</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="G4" s="6">
+        <v>28000</v>
+      </c>
+      <c r="H4" s="6">
+        <v>16000</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="7">
         <v>20</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="7">
         <v>300</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="7">
         <v>30</v>
       </c>
-      <c r="M4" s="3">
-        <v>180</v>
-      </c>
-      <c r="N4" s="3">
-        <v>36</v>
-      </c>
-      <c r="O4" s="7">
+      <c r="M4" s="7">
+        <v>150</v>
+      </c>
+      <c r="N4" s="7">
+        <v>30</v>
+      </c>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="5">
         <v>2.5</v>
-      </c>
-      <c r="P4" s="7">
-        <v>2</v>
       </c>
       <c r="Q4" s="8">
         <v>0.72</v>
@@ -2016,29 +2030,65 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:18">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
+      <c r="A5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5">
+        <v>69.9</v>
+      </c>
+      <c r="D5" s="5">
+        <v>80</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F5" s="6">
+        <v>15</v>
+      </c>
+      <c r="G5" s="6">
+        <v>26000</v>
+      </c>
+      <c r="H5" s="6">
+        <v>12000</v>
+      </c>
+      <c r="I5" s="5">
+        <v>8</v>
+      </c>
+      <c r="J5" s="7">
+        <v>20</v>
+      </c>
+      <c r="K5" s="7">
+        <v>300</v>
+      </c>
+      <c r="L5" s="7">
+        <v>30</v>
+      </c>
+      <c r="M5" s="7">
+        <v>180</v>
+      </c>
+      <c r="N5" s="7">
+        <v>36</v>
+      </c>
+      <c r="O5" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:18">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
@@ -2055,10 +2105,12 @@
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
     </row>
-    <row r="7" s="6" customFormat="1" ht="22" customHeight="1" spans="1:18">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
+    <row r="7" ht="22" customHeight="1" spans="1:18">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="11"/>
@@ -2075,10 +2127,16 @@
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="1:18">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
+    <row r="8" s="1" customFormat="1" ht="22" customHeight="1" spans="1:18">
+      <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
@@ -2096,9 +2154,15 @@
       <c r="R8" s="13"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:18">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
+      <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="11"/>
@@ -2116,9 +2180,15 @@
       <c r="R9" s="13"/>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:18">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
@@ -2136,9 +2206,15 @@
       <c r="R10" s="13"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:18">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
+      <c r="A11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
@@ -2156,9 +2232,15 @@
       <c r="R11" s="13"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:18">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
+      <c r="A12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
@@ -2176,9 +2258,15 @@
       <c r="R12" s="13"/>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:18">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
+      <c r="A13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
@@ -2196,9 +2284,15 @@
       <c r="R13" s="13"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:18">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
+      <c r="A14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
@@ -2215,215 +2309,106 @@
       <c r="Q14" s="13"/>
       <c r="R14" s="13"/>
     </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
+    <row r="15" ht="22" customHeight="1" spans="1:18">
+      <c r="A15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
+      <c r="A16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
     </row>
-    <row r="18" s="6" customFormat="1" ht="24" customHeight="1" spans="1:3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+    <row r="18" ht="24" customHeight="1" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
-    <row r="19" ht="22" customHeight="1" spans="1:3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+    <row r="19" s="1" customFormat="1" ht="24" customHeight="1" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
+      <c r="A20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1800</v>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="A21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:3">
+      <c r="A22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="7">
+        <v>4</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3000</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A18:C18"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="2"/>
-  <sheetData>
-    <row r="1" ht="28" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="2"/>
-  <sheetData>
-    <row r="1" ht="42" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="3">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="3">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4">
-        <v>3000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>